--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.70282</v>
+        <v>17.00636</v>
       </c>
       <c r="D2" t="n">
-        <v>16.58452</v>
+        <v>16.54905</v>
       </c>
       <c r="E2" t="n">
-        <v>16.77371</v>
+        <v>16.82001</v>
       </c>
       <c r="F2" t="n">
-        <v>41.60555</v>
+        <v>43.21179</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05018</v>
+        <v>0.04971</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8101</v>
+        <v>1.84656</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.17609</v>
+        <v>16.97143</v>
       </c>
       <c r="D3" t="n">
-        <v>16.42727</v>
+        <v>16.53353</v>
       </c>
       <c r="E3" t="n">
-        <v>16.92558</v>
+        <v>16.61156</v>
       </c>
       <c r="F3" t="n">
-        <v>42.849</v>
+        <v>41.93424</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05031</v>
+        <v>0.05072</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84787</v>
+        <v>1.84331</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.97081</v>
+        <v>16.75294</v>
       </c>
       <c r="D4" t="n">
-        <v>16.63194</v>
+        <v>16.5332</v>
       </c>
       <c r="E4" t="n">
-        <v>17.00237</v>
+        <v>16.56517</v>
       </c>
       <c r="F4" t="n">
-        <v>42.7124</v>
+        <v>42.31991</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05078</v>
+        <v>0.05003</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7965</v>
+        <v>1.83817</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.82971</v>
+        <v>16.41441</v>
       </c>
       <c r="D6" t="n">
-        <v>16.03521</v>
+        <v>16.3687</v>
       </c>
       <c r="E6" t="n">
-        <v>16.49607</v>
+        <v>16.38588</v>
       </c>
       <c r="F6" t="n">
-        <v>21.6367</v>
+        <v>21.86961</v>
       </c>
       <c r="G6" t="n">
-        <v>34.11099</v>
+        <v>34.34281</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.40709</v>
+        <v>16.61353</v>
       </c>
       <c r="D7" t="n">
-        <v>15.96501</v>
+        <v>15.81002</v>
       </c>
       <c r="E7" t="n">
-        <v>16.6406</v>
+        <v>16.38166</v>
       </c>
       <c r="F7" t="n">
-        <v>21.8961</v>
+        <v>21.65727</v>
       </c>
       <c r="G7" t="n">
-        <v>34.23078</v>
+        <v>34.06757</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.65729</v>
+        <v>16.75093</v>
       </c>
       <c r="D8" t="n">
-        <v>16.00302</v>
+        <v>16.05386</v>
       </c>
       <c r="E8" t="n">
-        <v>16.50592</v>
+        <v>16.24882</v>
       </c>
       <c r="F8" t="n">
-        <v>21.2681</v>
+        <v>21.51256</v>
       </c>
       <c r="G8" t="n">
-        <v>34.77697</v>
+        <v>33.5648</v>
       </c>
     </row>
   </sheetData>
